--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_30_R3.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_30_R3.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5909</v>
+        <v>3.9112</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1349</v>
+        <v>4.4888</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.544</v>
+        <v>-0.5776</v>
       </c>
       <c r="G2" t="n">
         <v>1.098</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4195</v>
+        <v>-0.0993</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7468</v>
+        <v>-0.393</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3273</v>
+        <v>0.2937</v>
       </c>
       <c r="V2" t="n">
         <v>2.6805</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4352</v>
+        <v>3.4289</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4333</v>
+        <v>2.2589</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0019</v>
+        <v>1.17</v>
       </c>
       <c r="G3" t="n">
         <v>0.5111</v>
@@ -688,13 +688,13 @@
         <v>3.2473</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.661</v>
+        <v>-0.6673</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0218</v>
+        <v>-0.1962</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6392</v>
+        <v>-0.4711</v>
       </c>
       <c r="V3" t="n">
         <v>1.4975</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3819</v>
+        <v>1.6063</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6632</v>
+        <v>-0.2804</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7188</v>
+        <v>1.8868</v>
       </c>
       <c r="G4" t="n">
         <v>-3.8187</v>
@@ -766,13 +766,13 @@
         <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6234</v>
+        <v>-0.1522</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1053</v>
+        <v>0.1617</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4819</v>
+        <v>-0.3139</v>
       </c>
       <c r="V4" t="n">
         <v>3.7217</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3373</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2072</v>
+        <v>-0.744</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5445</v>
+        <v>1.2707</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0048</v>
+        <v>0.4868</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0587</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.5454</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0168</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>0.0168</v>
       </c>
       <c r="L5" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.0755</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4718</v>
+      </c>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
-        <v>-0.0216</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.0216</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.232</v>
-      </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2842</v>
+        <v>-0.8905</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.224</v>
+        <v>-0.5149</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0602</v>
+        <v>-0.3756</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3943</v>
+        <v>0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3943</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3251</v>
+        <v>0.3709</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.744</v>
+        <v>-0.2072</v>
       </c>
       <c r="F6" t="n">
-        <v>1.069</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4868</v>
+        <v>-0.0048</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0587</v>
+        <v>-0.0048</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5454</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0168</v>
       </c>
       <c r="K6" t="n">
         <v>0.0168</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0736</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3963</v>
+        <v>-0.0216</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0755</v>
+        <v>-0.0216</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4718</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-1.3917</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0921</v>
+        <v>-0.2506</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5149</v>
+        <v>-0.224</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5772</v>
+        <v>-0.0266</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9304</v>
+        <v>0.3943</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1418</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0785</v>
+        <v>-0.1121</v>
       </c>
       <c r="E7" t="n">
         <v>-1.0503</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9718</v>
+        <v>0.9382</v>
       </c>
       <c r="G7" t="n">
         <v>0.6477000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0303</v>
+        <v>-0.0639</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0668</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0365</v>
+        <v>0.0029</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4163</v>
+        <v>-0.7353</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1982</v>
+        <v>-1.0803</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7819</v>
+        <v>0.345</v>
       </c>
       <c r="G8" t="n">
         <v>0.5281</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1252</v>
+        <v>-0.1937</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2908</v>
+        <v>-0.1729</v>
       </c>
       <c r="U8" t="n">
-        <v>0.416</v>
+        <v>-0.0209</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-1.2731</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1276</v>
+        <v>-0.8353</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6058</v>
+        <v>-0.4377</v>
       </c>
       <c r="G9" t="n">
         <v>0.0687</v>
@@ -1156,13 +1156,13 @@
         <v>3.7112</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5522</v>
+        <v>-1.0919</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3189</v>
+        <v>-0.3888</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8711</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0.6778999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0745</v>
+        <v>-1.7137</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6597</v>
+        <v>-1.8956</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5851</v>
+        <v>0.1818</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1941</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7099</v>
+        <v>0.0707</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2513</v>
+        <v>-0.4872</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.5579</v>
       </c>
       <c r="V10" t="n">
         <v>-1.7501</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.497</v>
+        <v>-2.3119</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6356</v>
+        <v>-3.5176</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1386</v>
+        <v>1.2058</v>
       </c>
       <c r="G11" t="n">
         <v>0.5816</v>
@@ -1312,13 +1312,13 @@
         <v>2.5515</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0527</v>
+        <v>0.2379</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1608</v>
+        <v>-0.0428</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2135</v>
+        <v>0.2807</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9716</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.972</v>
+        <v>-6.3994</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.2641</v>
+        <v>-6.7923</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2921</v>
+        <v>0.3929</v>
       </c>
       <c r="G12" t="n">
         <v>-5.0392</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3245</v>
+        <v>-0.7519</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1123</v>
+        <v>-0.6405</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2122</v>
+        <v>-0.1114</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.701300000000001</v>
+        <v>-2.701500000000002</v>
       </c>
       <c r="E13" t="n">
         <v>-9.6553</v>
       </c>
       <c r="F13" t="n">
-        <v>6.953900000000001</v>
+        <v>6.954</v>
       </c>
       <c r="G13" t="n">
         <v>-6.1348</v>
@@ -1468,13 +1468,13 @@
         <v>19.716</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.8526</v>
+        <v>-3.8527</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.9653</v>
+        <v>-2.9654</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8873</v>
+        <v>-0.8874000000000002</v>
       </c>
       <c r="V13" t="n">
         <v>4.9666</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>D. MOTIEJUNAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1862</v>
+        <v>4.933</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4803</v>
+        <v>3.9827</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7059</v>
+        <v>0.9503</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2488</v>
+        <v>4.1865</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0442</v>
+        <v>3.7849</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2046</v>
+        <v>0.4016</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0271</v>
+        <v>3.2466</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9732</v>
+        <v>3.2097</v>
       </c>
       <c r="L14" t="n">
-        <v>1.0539</v>
+        <v>0.0368</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2218</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.5752</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1507</v>
+        <v>0.3648</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.7834</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>3.007</v>
+        <v>0.8393</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9505</v>
+        <v>0.3108</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0565</v>
+        <v>0.5285</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3943</v>
+        <v>-0.7886</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2862</v>
+        <v>0.4254</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.8919</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. MOTIEJUNAS</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.5671</v>
+        <v>4.3124</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5725</v>
+        <v>3.0649</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9947</v>
+        <v>1.2475</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1865</v>
+        <v>3.2488</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7849</v>
+        <v>2.0442</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4016</v>
+        <v>1.2046</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2466</v>
+        <v>3.0271</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2097</v>
+        <v>1.9732</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0368</v>
+        <v>1.0539</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.2218</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5752</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3648</v>
+        <v>0.1507</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.7834</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4734</v>
+        <v>1.1332</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9006</v>
+        <v>0.5351</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5729</v>
+        <v>0.5981</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7886</v>
+        <v>0.3943</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4254</v>
+        <v>2.2862</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.214</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>T. CARTER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6245</v>
+        <v>2.6358</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7883</v>
+        <v>-0.1589</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8362000000000001</v>
+        <v>2.7948</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3003</v>
+        <v>0.9948</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0193</v>
+        <v>-1.1767</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.281</v>
+        <v>2.1715</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1075</v>
+        <v>0.2585</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1443</v>
+        <v>-1.3942</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0368</v>
+        <v>1.6527</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1929</v>
+        <v>0.7363</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1249</v>
+        <v>0.2175</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3178</v>
+        <v>0.5188</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9997</v>
+        <v>0.0147</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6122</v>
+        <v>-0.098</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3875</v>
+        <v>0.1127</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4665</v>
+        <v>0.9304</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.2525</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. CARTER</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5813</v>
+        <v>0.9271</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3948</v>
+        <v>-1.2065</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9761</v>
+        <v>2.1336</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9948</v>
+        <v>-0.5317</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1767</v>
+        <v>2.6469</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1715</v>
+        <v>-3.1787</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2585</v>
+        <v>-0.239</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3942</v>
+        <v>1.9361</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6527</v>
+        <v>-2.175</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7363</v>
+        <v>-0.2928</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2175</v>
+        <v>0.7109</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5188</v>
+        <v>-1.0037</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>-1.8556</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0398</v>
+        <v>0.8531</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3339</v>
+        <v>-0.326</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7059</v>
+        <v>1.1791</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9304</v>
+        <v>0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3311</v>
+        <v>0.653</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1502</v>
+        <v>-0.2732</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8191</v>
+        <v>0.9263</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5317</v>
+        <v>-0.3003</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6469</v>
+        <v>-0.0193</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.1787</v>
+        <v>-0.281</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.239</v>
+        <v>-0.1075</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9361</v>
+        <v>-0.1443</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.175</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2928</v>
+        <v>-0.1929</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7109</v>
+        <v>0.1249</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0037</v>
+        <v>-0.3178</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8556</v>
+        <v>-0.4639</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.405</v>
+        <v>1.0282</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2696</v>
+        <v>0.5507</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8646</v>
+        <v>0.4775</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1418</v>
+        <v>-1.4665</v>
       </c>
       <c r="W18" t="n">
-        <v>1.214</v>
+        <v>-0.2525</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DAVIDOVAC</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8264</v>
+        <v>-0.3527</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5115</v>
+        <v>-3.1255</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6851</v>
+        <v>2.7728</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6246</v>
+        <v>3.6854</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7347</v>
+        <v>2.3035</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.89</v>
+        <v>1.3819</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3783</v>
+        <v>2.3201</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4887</v>
+        <v>1.7715</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1104</v>
+        <v>0.5486</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2464</v>
+        <v>1.3654</v>
       </c>
       <c r="N19" t="n">
-        <v>0.754</v>
+        <v>0.5321</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0004</v>
+        <v>0.8333</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4639</v>
+        <v>-4.871</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>2.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8008</v>
+        <v>0.0521</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1889</v>
+        <v>-0.322</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6119</v>
+        <v>0.3741</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9304</v>
+        <v>-2.0026</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>-0.2525</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4696</v>
+        <v>-0.5989</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1954</v>
+        <v>-1.6056</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7257</v>
+        <v>1.0066</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9161</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3369</v>
+        <v>0.5337</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7468</v>
+        <v>-0.1571</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4099</v>
+        <v>0.6908</v>
       </c>
       <c r="V20" t="n">
         <v>-1.6083</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>D. DAVIDOVAC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4973</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3614</v>
+        <v>-1.6294</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8641</v>
+        <v>0.8759</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6854</v>
+        <v>-1.6246</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3035</v>
+        <v>-0.7347</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3819</v>
+        <v>-0.89</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3201</v>
+        <v>-1.3783</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7715</v>
+        <v>-1.4887</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5486</v>
+        <v>0.1104</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3654</v>
+        <v>-0.2464</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5321</v>
+        <v>0.754</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8333</v>
+        <v>-1.0004</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.871</v>
+        <v>-0.4639</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7834</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0925</v>
+        <v>0.8738</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5579</v>
+        <v>0.0709</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5346</v>
+        <v>0.8028</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0026</v>
+        <v>-0.9304</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.2525</v>
+        <v>0.1418</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7501</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6593</v>
+        <v>-2.4405</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2943</v>
+        <v>-3.1764</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6351</v>
+        <v>0.7359</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8404</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4722</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1889</v>
+        <v>0.3068</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2834</v>
+        <v>0.3842</v>
       </c>
       <c r="V22" t="n">
         <v>4.116</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4741</v>
+        <v>-4.2553</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8875</v>
+        <v>-2.826</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5866</v>
+        <v>-1.4293</v>
       </c>
       <c r="G23" t="n">
         <v>0.2326</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0262</v>
+        <v>0.1926</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0455</v>
+        <v>0.016</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0193</v>
+        <v>0.1766</v>
       </c>
       <c r="V23" t="n">
         <v>-3.7527</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.7013</v>
+        <v>5.0604</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.954</v>
+        <v>-6.953900000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>9.655399999999998</v>
+        <v>12.0144</v>
       </c>
       <c r="G24" t="n">
         <v>6.134999999999999</v>
@@ -2305,7 +2305,7 @@
         <v>4.385</v>
       </c>
       <c r="L24" t="n">
-        <v>0.03269999999999951</v>
+        <v>0.03270000000000017</v>
       </c>
       <c r="M24" t="n">
         <v>1.7172</v>
@@ -2326,13 +2326,13 @@
         <v>17.3965</v>
       </c>
       <c r="S24" t="n">
-        <v>3.8527</v>
+        <v>6.2117</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8874000000000006</v>
+        <v>0.8872</v>
       </c>
       <c r="U24" t="n">
-        <v>2.9655</v>
+        <v>5.3244</v>
       </c>
       <c r="V24" t="n">
         <v>-4.9666</v>
